--- a/2026/ЗАВОДЫ/Останкино/филиалы НВ/09,26/16,09,26 Останкино СЫРЫ/дв 16,09,26 млрсч ост сыр.xlsx
+++ b/2026/ЗАВОДЫ/Останкино/филиалы НВ/09,26/16,09,26 Останкино СЫРЫ/дв 16,09,26 млрсч ост сыр.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\в бланки заводов\Останкино СЫР\OrderCheeseInForm\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\2026\ЗАВОДЫ\Останкино\филиалы НВ\09,26\16,09,26 Останкино СЫРЫ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F9F76BC-AFE4-48E8-A59E-1F570A97EB69}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E07DDD3-07BD-40F1-B328-416B3667E083}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -149,9 +149,6 @@
   </si>
   <si>
     <t>шт</t>
-  </si>
-  <si>
-    <t>10,09,26 - нет на заводе / 03,09,26 - нет на заводе / 30,07,26 - нет на заводе</t>
   </si>
   <si>
     <t>4421584 Спред растительно-сливочный "Сливочный вкус" 72,5% 180гр  Останкино</t>
@@ -333,6 +330,9 @@
   <si>
     <t>21,09,</t>
   </si>
+  <si>
+    <t>17,09,26 - нет на заводе / 10,09,26 - нет на заводе / 03,09,26 - нет на заводе / 30,07,26 - нет на заводе</t>
+  </si>
 </sst>
 </file>
 
@@ -384,7 +384,7 @@
       <charset val="204"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -416,6 +416,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -455,7 +461,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -476,6 +482,7 @@
     <xf numFmtId="164" fontId="6" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="7" borderId="2" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Arial10px" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
@@ -2764,13 +2771,13 @@
         <v>16</v>
       </c>
       <c r="R3" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="S3" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="T3" s="3" t="s">
         <v>94</v>
-      </c>
-      <c r="S3" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="T3" s="3" t="s">
-        <v>95</v>
       </c>
       <c r="U3" s="2" t="s">
         <v>17</v>
@@ -2856,10 +2863,10 @@
       <c r="Q4" s="1"/>
       <c r="R4" s="1"/>
       <c r="S4" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="T4" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="U4" s="1"/>
       <c r="V4" s="1"/>
@@ -2964,7 +2971,7 @@
       </c>
       <c r="S5" s="4">
         <f t="shared" si="0"/>
-        <v>4608</v>
+        <v>4512</v>
       </c>
       <c r="T5" s="4">
         <f t="shared" si="0"/>
@@ -3197,9 +3204,8 @@
       <c r="R7" s="5">
         <v>48</v>
       </c>
-      <c r="S7" s="5">
-        <f>VLOOKUP(A7,заказ!A:B,2,0)</f>
-        <v>48</v>
+      <c r="S7" s="20">
+        <v>0</v>
       </c>
       <c r="T7" s="18">
         <f>VLOOKUP(A7,[1]Sheet!$A:$R,18,0)</f>
@@ -3244,7 +3250,7 @@
         <v>0</v>
       </c>
       <c r="AG7" s="1" t="s">
-        <v>38</v>
+        <v>98</v>
       </c>
       <c r="AH7" s="1">
         <f t="shared" ref="AH7:AH51" si="6">G7*R7</f>
@@ -3270,7 +3276,7 @@
     </row>
     <row r="8" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>37</v>
@@ -3313,9 +3319,8 @@
       <c r="R8" s="5">
         <v>48</v>
       </c>
-      <c r="S8" s="5">
-        <f>VLOOKUP(A8,заказ!A:B,2,0)</f>
-        <v>48</v>
+      <c r="S8" s="20">
+        <v>0</v>
       </c>
       <c r="T8" s="18">
         <f>VLOOKUP(A8,[1]Sheet!$A:$R,18,0)</f>
@@ -3360,7 +3365,7 @@
         <v>0</v>
       </c>
       <c r="AG8" s="1" t="s">
-        <v>38</v>
+        <v>98</v>
       </c>
       <c r="AH8" s="1">
         <f t="shared" si="6"/>
@@ -3386,7 +3391,7 @@
     </row>
     <row r="9" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>34</v>
@@ -3476,7 +3481,7 @@
         <v>1.8504</v>
       </c>
       <c r="AG9" s="14" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH9" s="1">
         <f t="shared" si="6"/>
@@ -3502,7 +3507,7 @@
     </row>
     <row r="10" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>37</v>
@@ -3587,7 +3592,7 @@
         <v>0</v>
       </c>
       <c r="AG10" s="14" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH10" s="1">
         <f t="shared" si="6"/>
@@ -3613,7 +3618,7 @@
     </row>
     <row r="11" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>37</v>
@@ -3698,7 +3703,7 @@
         <v>10</v>
       </c>
       <c r="AG11" s="14" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH11" s="1">
         <f t="shared" si="6"/>
@@ -3724,7 +3729,7 @@
     </row>
     <row r="12" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>37</v>
@@ -3809,7 +3814,7 @@
         <v>6</v>
       </c>
       <c r="AG12" s="14" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AH12" s="1">
         <f t="shared" si="6"/>
@@ -3835,7 +3840,7 @@
     </row>
     <row r="13" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>37</v>
@@ -3944,7 +3949,7 @@
     </row>
     <row r="14" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>37</v>
@@ -4061,7 +4066,7 @@
     </row>
     <row r="15" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>37</v>
@@ -4146,7 +4151,7 @@
         <v>2.6</v>
       </c>
       <c r="AG15" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AH15" s="1">
         <f t="shared" si="6"/>
@@ -4172,7 +4177,7 @@
     </row>
     <row r="16" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>37</v>
@@ -4283,7 +4288,7 @@
     </row>
     <row r="17" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>37</v>
@@ -4394,7 +4399,7 @@
     </row>
     <row r="18" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>37</v>
@@ -4503,7 +4508,7 @@
     </row>
     <row r="19" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>37</v>
@@ -4618,7 +4623,7 @@
     </row>
     <row r="20" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>37</v>
@@ -4735,7 +4740,7 @@
     </row>
     <row r="21" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>37</v>
@@ -4852,7 +4857,7 @@
     </row>
     <row r="22" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>37</v>
@@ -4963,7 +4968,7 @@
     </row>
     <row r="23" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>37</v>
@@ -5077,7 +5082,7 @@
     </row>
     <row r="24" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>37</v>
@@ -5192,7 +5197,7 @@
     </row>
     <row r="25" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>37</v>
@@ -5275,7 +5280,7 @@
         <v>0</v>
       </c>
       <c r="AG25" s="14" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AH25" s="1">
         <f t="shared" si="6"/>
@@ -5301,7 +5306,7 @@
     </row>
     <row r="26" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>34</v>
@@ -5380,7 +5385,7 @@
         <v>0.65100000000000002</v>
       </c>
       <c r="AG26" s="14" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="AH26" s="1">
         <f t="shared" si="6"/>
@@ -5406,7 +5411,7 @@
     </row>
     <row r="27" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A27" s="9" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B27" s="9" t="s">
         <v>34</v>
@@ -5483,7 +5488,7 @@
         <v>0</v>
       </c>
       <c r="AG27" s="16" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AH27" s="1">
         <f t="shared" si="6"/>
@@ -5509,7 +5514,7 @@
     </row>
     <row r="28" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>37</v>
@@ -5626,7 +5631,7 @@
     </row>
     <row r="29" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>37</v>
@@ -5741,7 +5746,7 @@
     </row>
     <row r="30" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>37</v>
@@ -5856,7 +5861,7 @@
     </row>
     <row r="31" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>37</v>
@@ -5971,7 +5976,7 @@
     </row>
     <row r="32" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>37</v>
@@ -6061,7 +6066,7 @@
         <v>47.2</v>
       </c>
       <c r="AG32" s="15" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AH32" s="1">
         <f t="shared" si="6"/>
@@ -6087,7 +6092,7 @@
     </row>
     <row r="33" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>37</v>
@@ -6196,7 +6201,7 @@
     </row>
     <row r="34" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>37</v>
@@ -6313,7 +6318,7 @@
     </row>
     <row r="35" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>37</v>
@@ -6428,7 +6433,7 @@
     </row>
     <row r="36" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>37</v>
@@ -6545,7 +6550,7 @@
     </row>
     <row r="37" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>37</v>
@@ -6630,7 +6635,7 @@
         <v>38.6</v>
       </c>
       <c r="AG37" s="15" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="AH37" s="1">
         <f t="shared" si="6"/>
@@ -6656,7 +6661,7 @@
     </row>
     <row r="38" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>37</v>
@@ -6773,7 +6778,7 @@
     </row>
     <row r="39" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>37</v>
@@ -6888,7 +6893,7 @@
     </row>
     <row r="40" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>34</v>
@@ -6973,7 +6978,7 @@
         <v>4.7187999999999999</v>
       </c>
       <c r="AG40" s="14" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH40" s="1">
         <f t="shared" si="6"/>
@@ -6999,7 +7004,7 @@
     </row>
     <row r="41" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>34</v>
@@ -7084,7 +7089,7 @@
         <v>1.9652000000000001</v>
       </c>
       <c r="AG41" s="14" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH41" s="1">
         <f t="shared" si="6"/>
@@ -7110,7 +7115,7 @@
     </row>
     <row r="42" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>34</v>
@@ -7227,7 +7232,7 @@
     </row>
     <row r="43" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>34</v>
@@ -7338,7 +7343,7 @@
     </row>
     <row r="44" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>37</v>
@@ -7431,7 +7436,7 @@
         <v>14.6</v>
       </c>
       <c r="AG44" s="15" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="AH44" s="1">
         <f t="shared" si="6"/>
@@ -7457,7 +7462,7 @@
     </row>
     <row r="45" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>37</v>
@@ -7572,7 +7577,7 @@
     </row>
     <row r="46" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>37</v>
@@ -7689,7 +7694,7 @@
     </row>
     <row r="47" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>37</v>
@@ -7796,7 +7801,7 @@
     </row>
     <row r="48" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>34</v>
@@ -7881,7 +7886,7 @@
         <v>2.528</v>
       </c>
       <c r="AG48" s="14" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH48" s="1">
         <f t="shared" si="6"/>
@@ -7907,7 +7912,7 @@
     </row>
     <row r="49" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A49" s="9" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B49" s="9" t="s">
         <v>37</v>
@@ -7927,10 +7932,10 @@
       </c>
       <c r="H49" s="9"/>
       <c r="I49" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="J49" s="9" t="s">
         <v>84</v>
-      </c>
-      <c r="J49" s="9" t="s">
-        <v>85</v>
       </c>
       <c r="K49" s="9"/>
       <c r="L49" s="9">
@@ -8014,7 +8019,7 @@
     </row>
     <row r="50" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>37</v>
@@ -8128,7 +8133,7 @@
     </row>
     <row r="51" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>34</v>
@@ -8217,7 +8222,7 @@
         <v>17.745999999999999</v>
       </c>
       <c r="AG51" s="15" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AH51" s="1">
         <f t="shared" si="6"/>
@@ -31961,7 +31966,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B3">
         <v>48</v>
@@ -31969,7 +31974,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B4">
         <v>16</v>
@@ -31977,7 +31982,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B5">
         <v>84</v>
@@ -31985,7 +31990,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B6">
         <v>16</v>
@@ -31993,7 +31998,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B7">
         <v>1700</v>
@@ -32001,7 +32006,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B8">
         <v>1000</v>
@@ -32009,7 +32014,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B9">
         <v>32</v>
@@ -32017,7 +32022,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B10">
         <v>60</v>
@@ -32025,7 +32030,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B11">
         <v>72</v>
@@ -32033,7 +32038,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B12">
         <v>40</v>
@@ -32041,7 +32046,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B13">
         <v>88</v>
@@ -32049,7 +32054,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B14">
         <v>100</v>
@@ -32057,7 +32062,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B15">
         <v>150</v>
@@ -32065,7 +32070,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B16">
         <v>100</v>
@@ -32073,7 +32078,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B17">
         <v>250</v>
@@ -32081,7 +32086,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B18">
         <v>32</v>
@@ -32089,7 +32094,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B19">
         <v>96</v>
@@ -32097,7 +32102,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B20">
         <v>148</v>
@@ -32105,7 +32110,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B21">
         <v>150</v>
@@ -32113,7 +32118,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B22">
         <v>120</v>
@@ -32121,7 +32126,7 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B23">
         <v>48</v>
@@ -32129,7 +32134,7 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B24">
         <v>60</v>
